--- a/Field-trails/TAN-concentration-and-aplication-rate.xlsx
+++ b/Field-trails/TAN-concentration-and-aplication-rate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EA518A-9074-407E-81B0-134F8A3B62AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E54E7D2-67B2-4897-B528-DD66D5343DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="16">
   <si>
     <t>Trial</t>
   </si>
@@ -148,12 +148,15 @@
       <t>[mg/m2]</t>
     </r>
   </si>
+  <si>
+    <t>Data derrived from AgroScena Github</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,12 +171,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -196,11 +193,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -534,7 +533,9 @@
       <c r="I1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="1"/>
+      <c r="K1" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -611,11 +612,11 @@
         <f t="shared" si="1"/>
         <v>5204.0355000000009</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="3">
         <f>AVERAGE(G2:G4)</f>
         <v>5371.0291000000007</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="3">
         <f>_xlfn.STDEV.P(G2:G4)</f>
         <v>143.27759524673306</v>
       </c>
@@ -694,11 +695,11 @@
         <f t="shared" si="1"/>
         <v>5413.8215000000009</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="3">
         <f>AVERAGE(G5:G7)</f>
         <v>5218.4069333333346</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="3">
         <f>_xlfn.STDEV.P(G5:G7)</f>
         <v>165.71685179474727</v>
       </c>
@@ -777,11 +778,11 @@
         <f t="shared" si="1"/>
         <v>5525.0220000000008</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="3">
         <f>AVERAGE(G8:G10)</f>
         <v>5466.2699333333339</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="3">
         <f>_xlfn.STDEV.P(G8:G10)</f>
         <v>95.323158199510388</v>
       </c>
@@ -860,11 +861,11 @@
         <f t="shared" si="1"/>
         <v>4744.8207000000011</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="3">
         <f>AVERAGE(G11:G13)</f>
         <v>4393.2278333333343</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="3">
         <f>_xlfn.STDEV.P(G11:G13)</f>
         <v>284.89664502343487</v>
       </c>
@@ -943,11 +944,11 @@
         <f t="shared" si="1"/>
         <v>4689.5384000000004</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="3">
         <f>AVERAGE(G14:G16)</f>
         <v>4650.4423666666671</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="3">
         <f>_xlfn.STDEV.P(G14:G16)</f>
         <v>91.635119057790916</v>
       </c>
@@ -1026,11 +1027,11 @@
         <f t="shared" si="1"/>
         <v>4663.2734</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="3">
         <f>AVERAGE(G17:G19)</f>
         <v>4741.8247333333338</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="3">
         <f>_xlfn.STDEV.P(G17:G19)</f>
         <v>112.22503828639238</v>
       </c>
@@ -1109,11 +1110,11 @@
         <f t="shared" si="1"/>
         <v>4911.6349</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="3">
         <f>AVERAGE(G20:G22)</f>
         <v>4867.4439666666667</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="3">
         <f>_xlfn.STDEV.P(G20:G22)</f>
         <v>77.584592256209021</v>
       </c>

--- a/Field-trails/TAN-concentration-and-aplication-rate.xlsx
+++ b/Field-trails/TAN-concentration-and-aplication-rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E54E7D2-67B2-4897-B528-DD66D5343DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F58DC15-0D47-444C-9511-C6708A8D6D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -193,12 +193,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -533,7 +532,7 @@
       <c r="I1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="1"/>
@@ -612,11 +611,11 @@
         <f t="shared" si="1"/>
         <v>5204.0355000000009</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <f>AVERAGE(G2:G4)</f>
         <v>5371.0291000000007</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <f>_xlfn.STDEV.P(G2:G4)</f>
         <v>143.27759524673306</v>
       </c>
@@ -695,11 +694,11 @@
         <f t="shared" si="1"/>
         <v>5413.8215000000009</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <f>AVERAGE(G5:G7)</f>
         <v>5218.4069333333346</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="2">
         <f>_xlfn.STDEV.P(G5:G7)</f>
         <v>165.71685179474727</v>
       </c>
@@ -778,11 +777,11 @@
         <f t="shared" si="1"/>
         <v>5525.0220000000008</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <f>AVERAGE(G8:G10)</f>
         <v>5466.2699333333339</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="2">
         <f>_xlfn.STDEV.P(G8:G10)</f>
         <v>95.323158199510388</v>
       </c>
@@ -861,11 +860,11 @@
         <f t="shared" si="1"/>
         <v>4744.8207000000011</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <f>AVERAGE(G11:G13)</f>
         <v>4393.2278333333343</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="2">
         <f>_xlfn.STDEV.P(G11:G13)</f>
         <v>284.89664502343487</v>
       </c>
@@ -944,11 +943,11 @@
         <f t="shared" si="1"/>
         <v>4689.5384000000004</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <f>AVERAGE(G14:G16)</f>
         <v>4650.4423666666671</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="2">
         <f>_xlfn.STDEV.P(G14:G16)</f>
         <v>91.635119057790916</v>
       </c>
@@ -1027,11 +1026,11 @@
         <f t="shared" si="1"/>
         <v>4663.2734</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="2">
         <f>AVERAGE(G17:G19)</f>
         <v>4741.8247333333338</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="2">
         <f>_xlfn.STDEV.P(G17:G19)</f>
         <v>112.22503828639238</v>
       </c>
@@ -1110,11 +1109,11 @@
         <f t="shared" si="1"/>
         <v>4911.6349</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="2">
         <f>AVERAGE(G20:G22)</f>
         <v>4867.4439666666667</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="2">
         <f>_xlfn.STDEV.P(G20:G22)</f>
         <v>77.584592256209021</v>
       </c>

--- a/Field-trails/TAN-concentration-and-aplication-rate.xlsx
+++ b/Field-trails/TAN-concentration-and-aplication-rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F58DC15-0D47-444C-9511-C6708A8D6D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7992FA78-A176-4CFB-94E5-3E0FE14AB35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -583,7 +583,7 @@
         <v>1.9151419999999999</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G22" si="1">E3*F3*10^3</f>
+        <f>E3*F3*10^3</f>
         <v>5553.9118000000008</v>
       </c>
     </row>
@@ -608,7 +608,7 @@
         <v>1.794495</v>
       </c>
       <c r="G4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="G3:G22" si="1">E4*F4*10^3</f>
         <v>5204.0355000000009</v>
       </c>
       <c r="H4" s="2">

--- a/Field-trails/TAN-concentration-and-aplication-rate.xlsx
+++ b/Field-trails/TAN-concentration-and-aplication-rate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7992FA78-A176-4CFB-94E5-3E0FE14AB35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EE136B-A250-463A-92A1-C390B17B4EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -84,10 +84,6 @@
     <t>Date (y-m-d)</t>
   </si>
   <si>
-    <t>Ammonium-N [g/L]
-Tveskæg</t>
-  </si>
-  <si>
     <t>Slurry Amount [Ton/ha]</t>
   </si>
   <si>
@@ -150,6 +146,9 @@
   </si>
   <si>
     <t>Data derrived from AgroScena Github</t>
+  </si>
+  <si>
+    <t>Ammonium m-N [g/ L] spec kit</t>
   </si>
 </sst>
 </file>
@@ -515,25 +514,25 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" t="s">
         <v>14</v>
-      </c>
-      <c r="K1" t="s">
-        <v>15</v>
       </c>
       <c r="L1" s="1"/>
     </row>
@@ -555,11 +554,11 @@
         <v>2.9000000000000004</v>
       </c>
       <c r="F2">
-        <v>1.8466</v>
+        <v>2.1781219749999998</v>
       </c>
       <c r="G2">
         <f>E2*F2*10^3</f>
-        <v>5355.14</v>
+        <v>6316.5537275000006</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -580,11 +579,11 @@
         <v>2.9000000000000004</v>
       </c>
       <c r="F3">
-        <v>1.9151419999999999</v>
+        <v>2.1235521240000002</v>
       </c>
       <c r="G3">
         <f>E3*F3*10^3</f>
-        <v>5553.9118000000008</v>
+        <v>6158.3011596000015</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -605,19 +604,19 @@
         <v>2.9000000000000004</v>
       </c>
       <c r="F4">
-        <v>1.794495</v>
+        <v>2.0775623269999999</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G3:G22" si="1">E4*F4*10^3</f>
-        <v>5204.0355000000009</v>
+        <f>E4*F4*10^3</f>
+        <v>6024.9307483000002</v>
       </c>
       <c r="H4" s="2">
         <f>AVERAGE(G2:G4)</f>
-        <v>5371.0291000000007</v>
+        <v>6166.5952118000014</v>
       </c>
       <c r="I4" s="2">
         <f>_xlfn.STDEV.P(G2:G4)</f>
-        <v>143.27759524673306</v>
+        <v>119.19894847353086</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -638,11 +637,11 @@
         <v>2.9000000000000004</v>
       </c>
       <c r="F5">
-        <v>1.8043929999999999</v>
+        <v>2.0696142989999999</v>
       </c>
       <c r="G5">
-        <f t="shared" si="1"/>
-        <v>5232.739700000001</v>
+        <f t="shared" ref="G4:G22" si="1">E5*F5*10^3</f>
+        <v>6001.8814671000009</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -663,11 +662,11 @@
         <v>2.9000000000000004</v>
       </c>
       <c r="F6">
-        <v>1.7271240000000001</v>
+        <v>2.2058823529999998</v>
       </c>
       <c r="G6">
         <f t="shared" si="1"/>
-        <v>5008.6596000000009</v>
+        <v>6397.0588237000002</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
@@ -688,19 +687,19 @@
         <v>2.9000000000000004</v>
       </c>
       <c r="F7">
-        <v>1.866835</v>
+        <v>2.1978021980000002</v>
       </c>
       <c r="G7">
         <f t="shared" si="1"/>
-        <v>5413.8215000000009</v>
+        <v>6373.626374200001</v>
       </c>
       <c r="H7" s="2">
         <f>AVERAGE(G5:G7)</f>
-        <v>5218.4069333333346</v>
+        <v>6257.5222216666671</v>
       </c>
       <c r="I7" s="2">
         <f>_xlfn.STDEV.P(G5:G7)</f>
-        <v>165.71685179474727</v>
+        <v>181.01826145254597</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -721,11 +720,11 @@
         <v>2.9000000000000004</v>
       </c>
       <c r="F8">
-        <v>1.8385579999999999</v>
+        <v>2.1329365079999998</v>
       </c>
       <c r="G8">
         <f t="shared" si="1"/>
-        <v>5331.8182000000006</v>
+        <v>6185.5158732</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -746,11 +745,11 @@
         <v>2.9000000000000004</v>
       </c>
       <c r="F9">
-        <v>1.9110240000000001</v>
+        <v>2.1697203470000002</v>
       </c>
       <c r="G9">
         <f t="shared" si="1"/>
-        <v>5541.9696000000004</v>
+        <v>6292.189006300001</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -771,19 +770,19 @@
         <v>2.9000000000000004</v>
       </c>
       <c r="F10">
-        <v>1.9051800000000001</v>
+        <v>2.166064982</v>
       </c>
       <c r="G10">
         <f t="shared" si="1"/>
-        <v>5525.0220000000008</v>
+        <v>6281.5884478000007</v>
       </c>
       <c r="H10" s="2">
         <f>AVERAGE(G8:G10)</f>
-        <v>5466.2699333333339</v>
+        <v>6253.0977757666669</v>
       </c>
       <c r="I10" s="2">
         <f>_xlfn.STDEV.P(G8:G10)</f>
-        <v>95.323158199510388</v>
+        <v>47.983178483199438</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
@@ -804,11 +803,11 @@
         <v>1.7000000000000002</v>
       </c>
       <c r="F11">
-        <v>2.5810770000000001</v>
+        <v>3.6077705830000002</v>
       </c>
       <c r="G11">
         <f t="shared" si="1"/>
-        <v>4387.8309000000008</v>
+        <v>6133.2099911000014</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
@@ -829,11 +828,11 @@
         <v>1.7000000000000002</v>
       </c>
       <c r="F12">
-        <v>2.3806069999999999</v>
+        <v>3.553800592</v>
       </c>
       <c r="G12">
         <f t="shared" si="1"/>
-        <v>4047.0319000000004</v>
+        <v>6041.4610064000008</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -854,19 +853,19 @@
         <v>1.7000000000000002</v>
       </c>
       <c r="F13">
-        <v>2.7910710000000001</v>
+        <v>3.8297872339999999</v>
       </c>
       <c r="G13">
         <f t="shared" si="1"/>
-        <v>4744.8207000000011</v>
+        <v>6510.6382978000011</v>
       </c>
       <c r="H13" s="2">
         <f>AVERAGE(G11:G13)</f>
-        <v>4393.2278333333343</v>
+        <v>6228.4364317666668</v>
       </c>
       <c r="I13" s="2">
         <f>_xlfn.STDEV.P(G11:G13)</f>
-        <v>284.89664502343487</v>
+        <v>203.03183484844897</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -887,11 +886,11 @@
         <v>1.7000000000000002</v>
       </c>
       <c r="F14">
-        <v>2.661114</v>
+        <v>3.673986486</v>
       </c>
       <c r="G14">
         <f t="shared" si="1"/>
-        <v>4523.8938000000007</v>
+        <v>6245.7770262000004</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
@@ -912,11 +911,11 @@
         <v>1.7000000000000002</v>
       </c>
       <c r="F15">
-        <v>2.7869969999999999</v>
+        <v>3.7213740460000002</v>
       </c>
       <c r="G15">
         <f t="shared" si="1"/>
-        <v>4737.8949000000002</v>
+        <v>6326.3358782000014</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
@@ -937,19 +936,19 @@
         <v>1.7000000000000002</v>
       </c>
       <c r="F16">
-        <v>2.7585519999999999</v>
+        <v>3.6320754719999999</v>
       </c>
       <c r="G16">
         <f t="shared" si="1"/>
-        <v>4689.5384000000004</v>
+        <v>6174.5283024000009</v>
       </c>
       <c r="H16" s="2">
         <f>AVERAGE(G14:G16)</f>
-        <v>4650.4423666666671</v>
+        <v>6248.8804022666673</v>
       </c>
       <c r="I16" s="2">
         <f>_xlfn.STDEV.P(G14:G16)</f>
-        <v>91.635119057790916</v>
+        <v>62.014021128701707</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -970,11 +969,11 @@
         <v>1.7000000000000002</v>
       </c>
       <c r="F17">
-        <v>2.882666</v>
+        <v>3.6150712829999998</v>
       </c>
       <c r="G17">
         <f t="shared" si="1"/>
-        <v>4900.5322000000006</v>
+        <v>6145.6211811000003</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -995,11 +994,11 @@
         <v>1.7000000000000002</v>
       </c>
       <c r="F18">
-        <v>2.7421579999999999</v>
+        <v>3.6683417089999999</v>
       </c>
       <c r="G18">
         <f t="shared" si="1"/>
-        <v>4661.6686000000009</v>
+        <v>6236.1809053000006</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -1020,19 +1019,19 @@
         <v>1.7000000000000002</v>
       </c>
       <c r="F19">
-        <v>2.7431019999999999</v>
+        <v>3.5074045210000002</v>
       </c>
       <c r="G19">
         <f t="shared" si="1"/>
-        <v>4663.2734</v>
+        <v>5962.5876857000012</v>
       </c>
       <c r="H19" s="2">
         <f>AVERAGE(G17:G19)</f>
-        <v>4741.8247333333338</v>
+        <v>6114.7965907000007</v>
       </c>
       <c r="I19" s="2">
         <f>_xlfn.STDEV.P(G17:G19)</f>
-        <v>112.22503828639238</v>
+        <v>113.80078787884609</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -1053,11 +1052,11 @@
         <v>1.7000000000000002</v>
       </c>
       <c r="F20">
-        <v>2.9013659999999999</v>
+        <v>3.692905734</v>
       </c>
       <c r="G20">
         <f t="shared" si="1"/>
-        <v>4932.3222000000005</v>
+        <v>6277.9397478000001</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1078,11 +1077,11 @@
         <v>1.7000000000000002</v>
       </c>
       <c r="F21">
-        <v>2.7990439999999999</v>
+        <v>3.6764705879999999</v>
       </c>
       <c r="G21">
         <f t="shared" si="1"/>
-        <v>4758.3748000000005</v>
+        <v>6249.9999996000006</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1103,19 +1102,19 @@
         <v>1.7000000000000002</v>
       </c>
       <c r="F22">
-        <v>2.8891969999999998</v>
+        <v>3.5928143709999998</v>
       </c>
       <c r="G22">
         <f t="shared" si="1"/>
-        <v>4911.6349</v>
+        <v>6107.7844307000005</v>
       </c>
       <c r="H22" s="2">
         <f>AVERAGE(G20:G22)</f>
-        <v>4867.4439666666667</v>
+        <v>6211.9080593666667</v>
       </c>
       <c r="I22" s="2">
         <f>_xlfn.STDEV.P(G20:G22)</f>
-        <v>77.584592256209021</v>
+        <v>74.504831688534338</v>
       </c>
     </row>
   </sheetData>

--- a/Field-trails/TAN-concentration-and-aplication-rate.xlsx
+++ b/Field-trails/TAN-concentration-and-aplication-rate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97EE136B-A250-463A-92A1-C390B17B4EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F821B7-0800-4FD5-A76B-1308645F7679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -105,32 +105,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>avg</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> [mg/m2]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">AmmoniumN application rate </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">stdev </t>
     </r>
     <r>
@@ -149,6 +123,9 @@
   </si>
   <si>
     <t>Ammonium m-N [g/ L] spec kit</t>
+  </si>
+  <si>
+    <t>AmmoniumN application rate mean [mg/m2]</t>
   </si>
 </sst>
 </file>
@@ -520,19 +497,19 @@
         <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" t="s">
         <v>13</v>
-      </c>
-      <c r="K1" t="s">
-        <v>14</v>
       </c>
       <c r="L1" s="1"/>
     </row>
@@ -640,7 +617,7 @@
         <v>2.0696142989999999</v>
       </c>
       <c r="G5">
-        <f t="shared" ref="G4:G22" si="1">E5*F5*10^3</f>
+        <f t="shared" ref="G5:G22" si="1">E5*F5*10^3</f>
         <v>6001.8814671000009</v>
       </c>
     </row>
@@ -667,6 +644,10 @@
       <c r="G6">
         <f t="shared" si="1"/>
         <v>6397.0588237000002</v>
+      </c>
+      <c r="K6">
+        <f>AVERAGE(G2:G22)</f>
+        <v>6211.6052419047619</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">

--- a/Field-trails/TAN-concentration-and-aplication-rate.xlsx
+++ b/Field-trails/TAN-concentration-and-aplication-rate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F821B7-0800-4FD5-A76B-1308645F7679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4246A580-80A5-4593-99BD-0610B15522EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="18">
   <si>
     <t>Trial</t>
   </si>
@@ -126,6 +126,12 @@
   </si>
   <si>
     <t>AmmoniumN application rate mean [mg/m2]</t>
+  </si>
+  <si>
+    <t>AmmoniumN application rate [kg/ ha]</t>
+  </si>
+  <si>
+    <t>mean</t>
   </si>
 </sst>
 </file>
@@ -470,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -480,7 +486,7 @@
     <col min="6" max="9" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -508,12 +514,14 @@
       <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="1"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -537,8 +545,19 @@
         <f>E2*F2*10^3</f>
         <v>6316.5537275000006</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L2">
+        <f>AVERAGE(G2:G10)</f>
+        <v>6225.7384030777785</v>
+      </c>
+      <c r="M2" s="2">
+        <f>L2/100</f>
+        <v>62.257384030777786</v>
+      </c>
+      <c r="N2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -562,8 +581,16 @@
         <f>E3*F3*10^3</f>
         <v>6158.3011596000015</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L3">
+        <f>_xlfn.STDEV.P(G2:G10)</f>
+        <v>134.82711051118892</v>
+      </c>
+      <c r="M3" s="2">
+        <f>L3/100</f>
+        <v>1.3482711051118892</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -595,8 +622,12 @@
         <f>_xlfn.STDEV.P(G2:G4)</f>
         <v>119.19894847353086</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="J4">
+        <f>H4*10^-6*10^4</f>
+        <v>61.665952118000007</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -621,7 +652,7 @@
         <v>6001.8814671000009</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -645,12 +676,8 @@
         <f t="shared" si="1"/>
         <v>6397.0588237000002</v>
       </c>
-      <c r="K6">
-        <f>AVERAGE(G2:G22)</f>
-        <v>6211.6052419047619</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -682,8 +709,12 @@
         <f>_xlfn.STDEV.P(G5:G7)</f>
         <v>181.01826145254597</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="J7">
+        <f>H7/100</f>
+        <v>62.575222216666674</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -708,7 +739,7 @@
         <v>6185.5158732</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -733,7 +764,7 @@
         <v>6292.189006300001</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -765,8 +796,12 @@
         <f>_xlfn.STDEV.P(G8:G10)</f>
         <v>47.983178483199438</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="J10">
+        <f>H10/100</f>
+        <v>62.530977757666669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -791,7 +826,7 @@
         <v>6133.2099911000014</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -816,7 +851,7 @@
         <v>6041.4610064000008</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -848,8 +883,12 @@
         <f>_xlfn.STDEV.P(G11:G13)</f>
         <v>203.03183484844897</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="J13">
+        <f>H13/100</f>
+        <v>62.284364317666672</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -874,7 +913,7 @@
         <v>6245.7770262000004</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -899,7 +938,7 @@
         <v>6326.3358782000014</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -931,8 +970,12 @@
         <f>_xlfn.STDEV.P(G14:G16)</f>
         <v>62.014021128701707</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J16">
+        <f>H16/100</f>
+        <v>62.48880402266667</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -957,7 +1000,7 @@
         <v>6145.6211811000003</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -982,7 +1025,7 @@
         <v>6236.1809053000006</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1014,8 +1057,12 @@
         <f>_xlfn.STDEV.P(G17:G19)</f>
         <v>113.80078787884609</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J19">
+        <f>H19/100</f>
+        <v>61.147965907000007</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1040,7 +1087,7 @@
         <v>6277.9397478000001</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1065,7 +1112,7 @@
         <v>6249.9999996000006</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1096,6 +1143,10 @@
       <c r="I22" s="2">
         <f>_xlfn.STDEV.P(G20:G22)</f>
         <v>74.504831688534338</v>
+      </c>
+      <c r="J22">
+        <f>H22/100</f>
+        <v>62.119080593666666</v>
       </c>
     </row>
   </sheetData>

--- a/Field-trails/TAN-concentration-and-aplication-rate.xlsx
+++ b/Field-trails/TAN-concentration-and-aplication-rate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4246A580-80A5-4593-99BD-0610B15522EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D7B65D7-F957-4435-A5F0-50D3188F9868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="20">
   <si>
     <t>Trial</t>
   </si>
@@ -132,6 +132,12 @@
   </si>
   <si>
     <t>mean</t>
+  </si>
+  <si>
+    <t>AmmoniumN application rate stdev [kg/ha]</t>
+  </si>
+  <si>
+    <t>=</t>
   </si>
 </sst>
 </file>
@@ -476,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -486,7 +492,7 @@
     <col min="6" max="9" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -517,11 +523,14 @@
       <c r="J1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -545,19 +554,19 @@
         <f>E2*F2*10^3</f>
         <v>6316.5537275000006</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <f>AVERAGE(G2:G10)</f>
         <v>6225.7384030777785</v>
       </c>
-      <c r="M2" s="2">
-        <f>L2/100</f>
+      <c r="N2" s="2">
+        <f>M2/100</f>
         <v>62.257384030777786</v>
       </c>
-      <c r="N2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -581,16 +590,16 @@
         <f>E3*F3*10^3</f>
         <v>6158.3011596000015</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <f>_xlfn.STDEV.P(G2:G10)</f>
         <v>134.82711051118892</v>
       </c>
-      <c r="M3" s="2">
-        <f>L3/100</f>
+      <c r="N3" s="2">
+        <f>M3/100</f>
         <v>1.3482711051118892</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -626,8 +635,12 @@
         <f>H4*10^-6*10^4</f>
         <v>61.665952118000007</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K4">
+        <f>I4/100</f>
+        <v>1.1919894847353085</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -652,7 +665,7 @@
         <v>6001.8814671000009</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -677,7 +690,7 @@
         <v>6397.0588237000002</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -713,8 +726,12 @@
         <f>H7/100</f>
         <v>62.575222216666674</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K7">
+        <f>I7/100</f>
+        <v>1.8101826145254598</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -739,7 +756,7 @@
         <v>6185.5158732</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -764,7 +781,7 @@
         <v>6292.189006300001</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -800,8 +817,12 @@
         <f>H10/100</f>
         <v>62.530977757666669</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K10">
+        <f>I10/100</f>
+        <v>0.4798317848319944</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -826,7 +847,7 @@
         <v>6133.2099911000014</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -851,7 +872,7 @@
         <v>6041.4610064000008</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -887,8 +908,12 @@
         <f>H13/100</f>
         <v>62.284364317666672</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K13">
+        <f>I13/100</f>
+        <v>2.0303183484844896</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -913,7 +938,7 @@
         <v>6245.7770262000004</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -938,7 +963,7 @@
         <v>6326.3358782000014</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -974,8 +999,12 @@
         <f>H16/100</f>
         <v>62.48880402266667</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K16">
+        <f>H16/100</f>
+        <v>62.48880402266667</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1000,7 +1029,7 @@
         <v>6145.6211811000003</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1025,7 +1054,7 @@
         <v>6236.1809053000006</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1061,8 +1090,11 @@
         <f>H19/100</f>
         <v>61.147965907000007</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1087,7 +1119,7 @@
         <v>6277.9397478000001</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1112,7 +1144,7 @@
         <v>6249.9999996000006</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>

--- a/Field-trails/TAN-concentration-and-aplication-rate.xlsx
+++ b/Field-trails/TAN-concentration-and-aplication-rate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D7B65D7-F957-4435-A5F0-50D3188F9868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D4C974-E71C-4238-8B2E-E7682C274351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
   <si>
     <t>Trial</t>
   </si>
@@ -136,14 +136,14 @@
   <si>
     <t>AmmoniumN application rate stdev [kg/ha]</t>
   </si>
-  <si>
-    <t>=</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -181,12 +181,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -490,6 +491,7 @@
     <col min="4" max="4" width="13.33203125" customWidth="1"/>
     <col min="5" max="5" width="13.33203125" style="1" customWidth="1"/>
     <col min="6" max="9" width="13.33203125" customWidth="1"/>
+    <col min="10" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
@@ -631,11 +633,11 @@
         <f>_xlfn.STDEV.P(G2:G4)</f>
         <v>119.19894847353086</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <f>H4*10^-6*10^4</f>
         <v>61.665952118000007</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="2">
         <f>I4/100</f>
         <v>1.1919894847353085</v>
       </c>
@@ -722,11 +724,11 @@
         <f>_xlfn.STDEV.P(G5:G7)</f>
         <v>181.01826145254597</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <f>H7/100</f>
         <v>62.575222216666674</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="2">
         <f>I7/100</f>
         <v>1.8101826145254598</v>
       </c>
@@ -813,11 +815,11 @@
         <f>_xlfn.STDEV.P(G8:G10)</f>
         <v>47.983178483199438</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="3">
         <f>H10/100</f>
         <v>62.530977757666669</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="3">
         <f>I10/100</f>
         <v>0.4798317848319944</v>
       </c>
@@ -904,14 +906,8 @@
         <f>_xlfn.STDEV.P(G11:G13)</f>
         <v>203.03183484844897</v>
       </c>
-      <c r="J13">
-        <f>H13/100</f>
-        <v>62.284364317666672</v>
-      </c>
-      <c r="K13">
-        <f>I13/100</f>
-        <v>2.0303183484844896</v>
-      </c>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -995,16 +991,8 @@
         <f>_xlfn.STDEV.P(G14:G16)</f>
         <v>62.014021128701707</v>
       </c>
-      <c r="J16">
-        <f>H16/100</f>
-        <v>62.48880402266667</v>
-      </c>
-      <c r="K16">
-        <f>H16/100</f>
-        <v>62.48880402266667</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1029,7 +1017,7 @@
         <v>6145.6211811000003</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1054,7 +1042,7 @@
         <v>6236.1809053000006</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1086,15 +1074,8 @@
         <f>_xlfn.STDEV.P(G17:G19)</f>
         <v>113.80078787884609</v>
       </c>
-      <c r="J19">
-        <f>H19/100</f>
-        <v>61.147965907000007</v>
-      </c>
-      <c r="K19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1119,7 +1100,7 @@
         <v>6277.9397478000001</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1144,7 +1125,7 @@
         <v>6249.9999996000006</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1175,10 +1156,6 @@
       <c r="I22" s="2">
         <f>_xlfn.STDEV.P(G20:G22)</f>
         <v>74.504831688534338</v>
-      </c>
-      <c r="J22">
-        <f>H22/100</f>
-        <v>62.119080593666666</v>
       </c>
     </row>
   </sheetData>

--- a/Field-trails/TAN-concentration-and-aplication-rate.xlsx
+++ b/Field-trails/TAN-concentration-and-aplication-rate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48D4C974-E71C-4238-8B2E-E7682C274351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{701FA6F9-3616-4F58-819F-B9574651EEBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -142,7 +142,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -187,7 +187,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/Field-trails/TAN-concentration-and-aplication-rate.xlsx
+++ b/Field-trails/TAN-concentration-and-aplication-rate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{701FA6F9-3616-4F58-819F-B9574651EEBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9BF91C-6418-4D3E-8983-DF22969B5104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,13 +128,13 @@
     <t>AmmoniumN application rate mean [mg/m2]</t>
   </si>
   <si>
-    <t>AmmoniumN application rate [kg/ ha]</t>
-  </si>
-  <si>
     <t>mean</t>
   </si>
   <si>
-    <t>AmmoniumN application rate stdev [kg/ha]</t>
+    <t>AmmoniumN application rate [kgN/ ha]</t>
+  </si>
+  <si>
+    <t>AmmoniumN application rate stdev [kgN/ha]</t>
   </si>
 </sst>
 </file>
@@ -181,13 +181,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -483,18 +484,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" customWidth="1"/>
     <col min="5" max="5" width="13.33203125" style="1" customWidth="1"/>
-    <col min="6" max="9" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="13.33203125" customWidth="1"/>
     <col min="10" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,7 +525,7 @@
         <v>12</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>18</v>
@@ -565,7 +567,7 @@
         <v>62.257384030777786</v>
       </c>
       <c r="O2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -633,11 +635,11 @@
         <f>_xlfn.STDEV.P(G2:G4)</f>
         <v>119.19894847353086</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="3">
         <f>H4*10^-6*10^4</f>
         <v>61.665952118000007</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="3">
         <f>I4/100</f>
         <v>1.1919894847353085</v>
       </c>
@@ -724,11 +726,11 @@
         <f>_xlfn.STDEV.P(G5:G7)</f>
         <v>181.01826145254597</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="3">
         <f>H7/100</f>
         <v>62.575222216666674</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="3">
         <f>I7/100</f>
         <v>1.8101826145254598</v>
       </c>
@@ -819,7 +821,7 @@
         <f>H10/100</f>
         <v>62.530977757666669</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="4">
         <f>I10/100</f>
         <v>0.4798317848319944</v>
       </c>
@@ -906,8 +908,14 @@
         <f>_xlfn.STDEV.P(G11:G13)</f>
         <v>203.03183484844897</v>
       </c>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="J13" s="3">
+        <f>H13/100</f>
+        <v>62.284364317666672</v>
+      </c>
+      <c r="K13" s="3">
+        <f>I13/100</f>
+        <v>2.0303183484844896</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -991,8 +999,16 @@
         <f>_xlfn.STDEV.P(G14:G16)</f>
         <v>62.014021128701707</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J16" s="3">
+        <f>H16/100</f>
+        <v>62.48880402266667</v>
+      </c>
+      <c r="K16" s="3">
+        <f>I16/100</f>
+        <v>0.62014021128701702</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1017,7 +1033,7 @@
         <v>6145.6211811000003</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1042,7 +1058,7 @@
         <v>6236.1809053000006</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1074,8 +1090,16 @@
         <f>_xlfn.STDEV.P(G17:G19)</f>
         <v>113.80078787884609</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J19" s="3">
+        <f>H19/100</f>
+        <v>61.147965907000007</v>
+      </c>
+      <c r="K19" s="3">
+        <f>I19/100</f>
+        <v>1.1380078787884609</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1100,7 +1124,7 @@
         <v>6277.9397478000001</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1125,7 +1149,7 @@
         <v>6249.9999996000006</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1156,6 +1180,20 @@
       <c r="I22" s="2">
         <f>_xlfn.STDEV.P(G20:G22)</f>
         <v>74.504831688534338</v>
+      </c>
+      <c r="J22" s="3">
+        <f>H22/100</f>
+        <v>62.119080593666666</v>
+      </c>
+      <c r="K22" s="3">
+        <f>I22/100</f>
+        <v>0.74504831688534334</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J25" s="2">
+        <f>AVERAGE(J4,J7,J10,J13,J16,J19,J22)</f>
+        <v>62.11605241904762</v>
       </c>
     </row>
   </sheetData>

--- a/Field-trails/TAN-concentration-and-aplication-rate.xlsx
+++ b/Field-trails/TAN-concentration-and-aplication-rate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Field-trails\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9BF91C-6418-4D3E-8983-DF22969B5104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD6E42E-A58C-4844-A7CA-BF8E3901A350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -635,7 +635,7 @@
         <f>_xlfn.STDEV.P(G2:G4)</f>
         <v>119.19894847353086</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <f>H4*10^-6*10^4</f>
         <v>61.665952118000007</v>
       </c>
@@ -726,7 +726,7 @@
         <f>_xlfn.STDEV.P(G5:G7)</f>
         <v>181.01826145254597</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <f>H7/100</f>
         <v>62.575222216666674</v>
       </c>
